--- a/data/trans_dic/P32E$casa_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,76; 80,9</t>
+          <t>44,22; 79,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 79,67</t>
+          <t>8,99; 83,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,57; 74,9</t>
+          <t>44,16; 75,9</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,84; 58,27</t>
+          <t>33,6; 56,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 53,33</t>
+          <t>19,65; 54,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,11; 53,46</t>
+          <t>34,18; 53,88</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,24; 78,69</t>
+          <t>42,52; 79,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 53,85</t>
+          <t>15,48; 57,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,68; 62,83</t>
+          <t>32,83; 60,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,79; 61,46</t>
+          <t>43,49; 61,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 48,39</t>
+          <t>21,94; 48,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,56; 54,26</t>
+          <t>39,76; 54,69</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12124; 21916</t>
+          <t>11979; 21611</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>430; 3964</t>
+          <t>447; 4140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13972; 24018</t>
+          <t>14160; 24337</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31910; 53373</t>
+          <t>30776; 52095</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4378; 12239</t>
+          <t>4508; 12406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39073; 61230</t>
+          <t>39151; 61710</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10421; 19885</t>
+          <t>10745; 20097</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3900; 14083</t>
+          <t>4049; 14937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16805; 32311</t>
+          <t>16882; 31216</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63028; 88466</t>
+          <t>62610; 88798</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12221; 26168</t>
+          <t>11866; 26266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78345; 107445</t>
+          <t>78738; 108303</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$casa_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,22; 79,78</t>
+          <t>45,29; 80,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 83,2</t>
+          <t>9,27; 90,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,16; 75,9</t>
+          <t>46,4; 75,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,6; 56,88</t>
+          <t>37,04; 60,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 54,06</t>
+          <t>19,17; 53,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 53,88</t>
+          <t>36,65; 54,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,52; 79,53</t>
+          <t>39,41; 79,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 57,11</t>
+          <t>18,64; 56,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,83; 60,7</t>
+          <t>33,98; 63,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,49; 61,69</t>
+          <t>45,44; 61,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 48,57</t>
+          <t>24,61; 48,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,76; 54,69</t>
+          <t>41,67; 55,7</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>21835</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11979; 21611</t>
+          <t>13208; 23414</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>447; 4140</t>
+          <t>541; 5255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14160; 24337</t>
+          <t>16237; 26593</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>60727</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30776; 52095</t>
+          <t>38721; 62745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4508; 12406</t>
+          <t>5762; 16008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39151; 61710</t>
+          <t>49328; 73678</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>26370</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10745; 20097</t>
+          <t>10609; 21305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4049; 14937</t>
+          <t>5141; 15546</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16882; 31216</t>
+          <t>18516; 34680</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74985</t>
+          <t>86227</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93576</t>
+          <t>108932</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62610; 88798</t>
+          <t>72984; 99464</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11866; 26266</t>
+          <t>15618; 31033</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78738; 108303</t>
+          <t>93370; 124807</t>
         </is>
       </c>
     </row>
